--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,62 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124964747</v>
+        <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gravertjärnen, Gravertjärnen, Dlr</t>
+          <t>Gravertjärnen Valsan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515866</v>
+        <v>515939</v>
       </c>
       <c r="R2" t="n">
-        <v>6721110</v>
+        <v>6721236</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,70 +775,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124964747</t>
+          <t>https://artportalen.se/Sighting/136934393</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124969191</v>
+        <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gravertjärnen, Gravertjärnen, Dlr</t>
+          <t>Gravertjärnen Valsan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515968</v>
+        <v>515998</v>
       </c>
       <c r="R3" t="n">
-        <v>6721156</v>
+        <v>6721216</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,27 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack.</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,69 +887,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124969191</t>
+          <t>https://artportalen.se/Sighting/136934394</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124964530</v>
+        <v>124964747</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -982,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515851</v>
+        <v>515866</v>
       </c>
       <c r="R4" t="n">
-        <v>6721114</v>
+        <v>6721110</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,12 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 20-30 bladrosetter.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,58 +1024,44 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124964530</t>
+          <t>https://artportalen.se/Sighting/124964747</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124964664</v>
+        <v>124969191</v>
       </c>
       <c r="B5" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1118,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515859</v>
+        <v>515968</v>
       </c>
       <c r="R5" t="n">
-        <v>6721106</v>
+        <v>6721156</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,7 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,13 +1146,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124964664</t>
+          <t>https://artportalen.se/Sighting/124969191</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124965078</v>
+        <v>124964530</v>
       </c>
       <c r="B6" t="n">
         <v>99118</v>
@@ -1225,17 +1182,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1249,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515902</v>
+        <v>515851</v>
       </c>
       <c r="R6" t="n">
-        <v>6721081</v>
+        <v>6721114</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1251,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Bladrosetter inom ca 5 kv dm</t>
+          <t>Ca 20-30 bladrosetter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,13 +1282,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124965078</t>
+          <t>https://artportalen.se/Sighting/124964530</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124965120</v>
+        <v>124964664</v>
       </c>
       <c r="B7" t="n">
         <v>99118</v>
@@ -1361,12 +1318,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1385,10 +1342,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515915</v>
+        <v>515859</v>
       </c>
       <c r="R7" t="n">
-        <v>6721080</v>
+        <v>6721106</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1420,7 +1377,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1430,12 +1387,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spridda över större yta.</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,13 +1413,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124965120</t>
+          <t>https://artportalen.se/Sighting/124964664</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124965474</v>
+        <v>124965078</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1497,17 +1449,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1521,10 +1473,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515949</v>
+        <v>515902</v>
       </c>
       <c r="R8" t="n">
-        <v>6721053</v>
+        <v>6721081</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1556,7 +1508,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1566,7 +1518,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bladrosetter inom ca 5 kv dm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1592,13 +1549,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124965474</t>
+          <t>https://artportalen.se/Sighting/124965078</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124965545</v>
+        <v>124965120</v>
       </c>
       <c r="B9" t="n">
         <v>99118</v>
@@ -1626,7 +1583,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1638,10 +1609,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515958</v>
+        <v>515915</v>
       </c>
       <c r="R9" t="n">
-        <v>6721041</v>
+        <v>6721080</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1673,7 +1644,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1683,7 +1654,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spridda över större yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1709,13 +1685,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124965545</t>
+          <t>https://artportalen.se/Sighting/124965120</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124965782</v>
+        <v>124965474</v>
       </c>
       <c r="B10" t="n">
         <v>99118</v>
@@ -1743,7 +1719,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1755,10 +1745,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515973</v>
+        <v>515949</v>
       </c>
       <c r="R10" t="n">
-        <v>6721037</v>
+        <v>6721053</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1826,13 +1816,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124965782</t>
+          <t>https://artportalen.se/Sighting/124965474</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124966149</v>
+        <v>124965545</v>
       </c>
       <c r="B11" t="n">
         <v>99118</v>
@@ -1872,10 +1862,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516021</v>
+        <v>515958</v>
       </c>
       <c r="R11" t="n">
-        <v>6721046</v>
+        <v>6721041</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1943,13 +1933,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124966149</t>
+          <t>https://artportalen.se/Sighting/124965545</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124969103</v>
+        <v>124965782</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1978,16 +1968,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gravertjärnen, Gravertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515969</v>
+        <v>515973</v>
       </c>
       <c r="R12" t="n">
-        <v>6721170</v>
+        <v>6721037</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2019,7 +2014,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2029,7 +2024,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2055,13 +2050,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124969103</t>
+          <t>https://artportalen.se/Sighting/124965782</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124969263</v>
+        <v>124966149</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -2090,16 +2085,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gravertjärnen, Gravertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515960</v>
+        <v>516021</v>
       </c>
       <c r="R13" t="n">
-        <v>6721167</v>
+        <v>6721046</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2167,13 +2167,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124969263</t>
+          <t>https://artportalen.se/Sighting/124966149</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124970766</v>
+        <v>124969103</v>
       </c>
       <c r="B14" t="n">
         <v>99118</v>
@@ -2204,14 +2204,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dunderberget, Dunderberget, Dlr</t>
+          <t>Gravertjärnen, Gravertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515681</v>
+        <v>515969</v>
       </c>
       <c r="R14" t="n">
-        <v>6721075</v>
+        <v>6721170</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2279,7 +2279,348 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/124969103</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124969263</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gravertjärnen, Gravertjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>515960</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6721167</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124969263</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124970766</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dunderberget, Dunderberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>515681</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6721075</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/124970766</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136934392</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>515821</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6721210</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>100 plantor</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136934392</t>
         </is>
       </c>
     </row>
@@ -2298,6 +2639,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35366-2026 artfynd.xlsx
+++ b/artfynd/A 35366-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934393</v>
       </c>
       <c r="B2" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136934394</v>
       </c>
       <c r="B3" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>136934392</v>
       </c>
       <c r="B17" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
